--- a/dataset/large/Delivery_Drones_Large_Dataset.xlsx
+++ b/dataset/large/Delivery_Drones_Large_Dataset.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/74f3fc933c58b622/Desktop/UATM/dataset/large/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="4" documentId="11_FFC65FC055D9AAC3D96AAFF1692C665360B5BAAC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E7891719-527B-49A1-A54A-7D539C03261A}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="611" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="611" uniqueCount="222">
   <si>
     <t>Drone_ID</t>
   </si>
@@ -140,13 +146,553 @@
   </si>
   <si>
     <t>South Bangalore</t>
+  </si>
+  <si>
+    <t>DRN_021</t>
+  </si>
+  <si>
+    <t>DRN_022</t>
+  </si>
+  <si>
+    <t>DRN_023</t>
+  </si>
+  <si>
+    <t>DRN_024</t>
+  </si>
+  <si>
+    <t>DRN_025</t>
+  </si>
+  <si>
+    <t>DRN_026</t>
+  </si>
+  <si>
+    <t>DRN_027</t>
+  </si>
+  <si>
+    <t>DRN_028</t>
+  </si>
+  <si>
+    <t>DRN_029</t>
+  </si>
+  <si>
+    <t>DRN_030</t>
+  </si>
+  <si>
+    <t>DRN_031</t>
+  </si>
+  <si>
+    <t>DRN_032</t>
+  </si>
+  <si>
+    <t>DRN_033</t>
+  </si>
+  <si>
+    <t>DRN_034</t>
+  </si>
+  <si>
+    <t>DRN_035</t>
+  </si>
+  <si>
+    <t>DRN_036</t>
+  </si>
+  <si>
+    <t>DRN_037</t>
+  </si>
+  <si>
+    <t>DRN_038</t>
+  </si>
+  <si>
+    <t>DRN_039</t>
+  </si>
+  <si>
+    <t>DRN_040</t>
+  </si>
+  <si>
+    <t>DRN_041</t>
+  </si>
+  <si>
+    <t>DRN_042</t>
+  </si>
+  <si>
+    <t>DRN_043</t>
+  </si>
+  <si>
+    <t>DRN_044</t>
+  </si>
+  <si>
+    <t>DRN_045</t>
+  </si>
+  <si>
+    <t>DRN_046</t>
+  </si>
+  <si>
+    <t>DRN_047</t>
+  </si>
+  <si>
+    <t>DRN_048</t>
+  </si>
+  <si>
+    <t>DRN_049</t>
+  </si>
+  <si>
+    <t>DRN_050</t>
+  </si>
+  <si>
+    <t>DRN_051</t>
+  </si>
+  <si>
+    <t>DRN_052</t>
+  </si>
+  <si>
+    <t>DRN_053</t>
+  </si>
+  <si>
+    <t>DRN_054</t>
+  </si>
+  <si>
+    <t>DRN_055</t>
+  </si>
+  <si>
+    <t>DRN_056</t>
+  </si>
+  <si>
+    <t>DRN_057</t>
+  </si>
+  <si>
+    <t>DRN_058</t>
+  </si>
+  <si>
+    <t>DRN_059</t>
+  </si>
+  <si>
+    <t>DRN_060</t>
+  </si>
+  <si>
+    <t>DRN_061</t>
+  </si>
+  <si>
+    <t>DRN_062</t>
+  </si>
+  <si>
+    <t>DRN_063</t>
+  </si>
+  <si>
+    <t>DRN_064</t>
+  </si>
+  <si>
+    <t>DRN_065</t>
+  </si>
+  <si>
+    <t>DRN_066</t>
+  </si>
+  <si>
+    <t>DRN_067</t>
+  </si>
+  <si>
+    <t>DRN_068</t>
+  </si>
+  <si>
+    <t>DRN_069</t>
+  </si>
+  <si>
+    <t>DRN_070</t>
+  </si>
+  <si>
+    <t>DRN_071</t>
+  </si>
+  <si>
+    <t>DRN_072</t>
+  </si>
+  <si>
+    <t>DRN_073</t>
+  </si>
+  <si>
+    <t>DRN_074</t>
+  </si>
+  <si>
+    <t>DRN_075</t>
+  </si>
+  <si>
+    <t>DRN_076</t>
+  </si>
+  <si>
+    <t>DRN_077</t>
+  </si>
+  <si>
+    <t>DRN_078</t>
+  </si>
+  <si>
+    <t>DRN_079</t>
+  </si>
+  <si>
+    <t>DRN_080</t>
+  </si>
+  <si>
+    <t>DRN_081</t>
+  </si>
+  <si>
+    <t>DRN_082</t>
+  </si>
+  <si>
+    <t>DRN_083</t>
+  </si>
+  <si>
+    <t>DRN_084</t>
+  </si>
+  <si>
+    <t>DRN_085</t>
+  </si>
+  <si>
+    <t>DRN_086</t>
+  </si>
+  <si>
+    <t>DRN_087</t>
+  </si>
+  <si>
+    <t>DRN_088</t>
+  </si>
+  <si>
+    <t>DRN_089</t>
+  </si>
+  <si>
+    <t>DRN_090</t>
+  </si>
+  <si>
+    <t>DRN_091</t>
+  </si>
+  <si>
+    <t>DRN_092</t>
+  </si>
+  <si>
+    <t>DRN_093</t>
+  </si>
+  <si>
+    <t>DRN_094</t>
+  </si>
+  <si>
+    <t>DRN_095</t>
+  </si>
+  <si>
+    <t>DRN_096</t>
+  </si>
+  <si>
+    <t>DRN_097</t>
+  </si>
+  <si>
+    <t>DRN_098</t>
+  </si>
+  <si>
+    <t>DRN_099</t>
+  </si>
+  <si>
+    <t>DRN_100</t>
+  </si>
+  <si>
+    <t>DRN_101</t>
+  </si>
+  <si>
+    <t>DRN_102</t>
+  </si>
+  <si>
+    <t>DRN_103</t>
+  </si>
+  <si>
+    <t>DRN_104</t>
+  </si>
+  <si>
+    <t>DRN_105</t>
+  </si>
+  <si>
+    <t>DRN_106</t>
+  </si>
+  <si>
+    <t>DRN_107</t>
+  </si>
+  <si>
+    <t>DRN_108</t>
+  </si>
+  <si>
+    <t>DRN_109</t>
+  </si>
+  <si>
+    <t>DRN_110</t>
+  </si>
+  <si>
+    <t>DRN_111</t>
+  </si>
+  <si>
+    <t>DRN_112</t>
+  </si>
+  <si>
+    <t>DRN_113</t>
+  </si>
+  <si>
+    <t>DRN_114</t>
+  </si>
+  <si>
+    <t>DRN_115</t>
+  </si>
+  <si>
+    <t>DRN_116</t>
+  </si>
+  <si>
+    <t>DRN_117</t>
+  </si>
+  <si>
+    <t>DRN_118</t>
+  </si>
+  <si>
+    <t>DRN_119</t>
+  </si>
+  <si>
+    <t>DRN_120</t>
+  </si>
+  <si>
+    <t>DRN_121</t>
+  </si>
+  <si>
+    <t>DRN_122</t>
+  </si>
+  <si>
+    <t>DRN_123</t>
+  </si>
+  <si>
+    <t>DRN_124</t>
+  </si>
+  <si>
+    <t>DRN_125</t>
+  </si>
+  <si>
+    <t>DRN_126</t>
+  </si>
+  <si>
+    <t>DRN_127</t>
+  </si>
+  <si>
+    <t>DRN_128</t>
+  </si>
+  <si>
+    <t>DRN_129</t>
+  </si>
+  <si>
+    <t>DRN_130</t>
+  </si>
+  <si>
+    <t>DRN_131</t>
+  </si>
+  <si>
+    <t>DRN_132</t>
+  </si>
+  <si>
+    <t>DRN_133</t>
+  </si>
+  <si>
+    <t>DRN_134</t>
+  </si>
+  <si>
+    <t>DRN_135</t>
+  </si>
+  <si>
+    <t>DRN_136</t>
+  </si>
+  <si>
+    <t>DRN_137</t>
+  </si>
+  <si>
+    <t>DRN_138</t>
+  </si>
+  <si>
+    <t>DRN_139</t>
+  </si>
+  <si>
+    <t>DRN_140</t>
+  </si>
+  <si>
+    <t>DRN_141</t>
+  </si>
+  <si>
+    <t>DRN_142</t>
+  </si>
+  <si>
+    <t>DRN_143</t>
+  </si>
+  <si>
+    <t>DRN_144</t>
+  </si>
+  <si>
+    <t>DRN_145</t>
+  </si>
+  <si>
+    <t>DRN_146</t>
+  </si>
+  <si>
+    <t>DRN_147</t>
+  </si>
+  <si>
+    <t>DRN_148</t>
+  </si>
+  <si>
+    <t>DRN_149</t>
+  </si>
+  <si>
+    <t>DRN_150</t>
+  </si>
+  <si>
+    <t>DRN_151</t>
+  </si>
+  <si>
+    <t>DRN_152</t>
+  </si>
+  <si>
+    <t>DRN_153</t>
+  </si>
+  <si>
+    <t>DRN_154</t>
+  </si>
+  <si>
+    <t>DRN_155</t>
+  </si>
+  <si>
+    <t>DRN_156</t>
+  </si>
+  <si>
+    <t>DRN_157</t>
+  </si>
+  <si>
+    <t>DRN_158</t>
+  </si>
+  <si>
+    <t>DRN_159</t>
+  </si>
+  <si>
+    <t>DRN_160</t>
+  </si>
+  <si>
+    <t>DRN_161</t>
+  </si>
+  <si>
+    <t>DRN_162</t>
+  </si>
+  <si>
+    <t>DRN_163</t>
+  </si>
+  <si>
+    <t>DRN_164</t>
+  </si>
+  <si>
+    <t>DRN_165</t>
+  </si>
+  <si>
+    <t>DRN_166</t>
+  </si>
+  <si>
+    <t>DRN_167</t>
+  </si>
+  <si>
+    <t>DRN_168</t>
+  </si>
+  <si>
+    <t>DRN_169</t>
+  </si>
+  <si>
+    <t>DRN_170</t>
+  </si>
+  <si>
+    <t>DRN_171</t>
+  </si>
+  <si>
+    <t>DRN_172</t>
+  </si>
+  <si>
+    <t>DRN_173</t>
+  </si>
+  <si>
+    <t>DRN_174</t>
+  </si>
+  <si>
+    <t>DRN_175</t>
+  </si>
+  <si>
+    <t>DRN_176</t>
+  </si>
+  <si>
+    <t>DRN_177</t>
+  </si>
+  <si>
+    <t>DRN_178</t>
+  </si>
+  <si>
+    <t>DRN_179</t>
+  </si>
+  <si>
+    <t>DRN_180</t>
+  </si>
+  <si>
+    <t>DRN_181</t>
+  </si>
+  <si>
+    <t>DRN_182</t>
+  </si>
+  <si>
+    <t>DRN_183</t>
+  </si>
+  <si>
+    <t>DRN_184</t>
+  </si>
+  <si>
+    <t>DRN_185</t>
+  </si>
+  <si>
+    <t>DRN_186</t>
+  </si>
+  <si>
+    <t>DRN_187</t>
+  </si>
+  <si>
+    <t>DRN_188</t>
+  </si>
+  <si>
+    <t>DRN_189</t>
+  </si>
+  <si>
+    <t>DRN_190</t>
+  </si>
+  <si>
+    <t>DRN_191</t>
+  </si>
+  <si>
+    <t>DRN_192</t>
+  </si>
+  <si>
+    <t>DRN_193</t>
+  </si>
+  <si>
+    <t>DRN_194</t>
+  </si>
+  <si>
+    <t>DRN_195</t>
+  </si>
+  <si>
+    <t>DRN_196</t>
+  </si>
+  <si>
+    <t>DRN_197</t>
+  </si>
+  <si>
+    <t>DRN_198</t>
+  </si>
+  <si>
+    <t>DRN_199</t>
+  </si>
+  <si>
+    <t>DRN_200</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -158,6 +704,12 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -209,13 +761,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -253,7 +813,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -287,6 +847,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -321,9 +882,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -496,11 +1058,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K201"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -535,12 +1097,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="B2">
-        <v>65.68000000000001</v>
+        <v>65.680000000000007</v>
       </c>
       <c r="C2">
         <v>79.16</v>
@@ -552,7 +1114,7 @@
         <v>31</v>
       </c>
       <c r="F2">
-        <v>90.09999999999999</v>
+        <v>90.1</v>
       </c>
       <c r="G2">
         <v>49</v>
@@ -561,15 +1123,15 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="B3">
-        <v>67.79000000000001</v>
+        <v>67.790000000000006</v>
       </c>
       <c r="C3">
-        <v>91.20999999999999</v>
+        <v>91.21</v>
       </c>
       <c r="D3">
         <v>0.87</v>
@@ -587,12 +1149,12 @@
         <v>38</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B4">
-        <v>82.23999999999999</v>
+        <v>82.24</v>
       </c>
       <c r="C4">
         <v>32.69</v>
@@ -613,9 +1175,9 @@
         <v>37</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="B5">
         <v>44.13</v>
@@ -630,7 +1192,7 @@
         <v>34</v>
       </c>
       <c r="F5">
-        <v>83.90000000000001</v>
+        <v>83.9</v>
       </c>
       <c r="G5">
         <v>59</v>
@@ -639,9 +1201,9 @@
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="B6">
         <v>27.17</v>
@@ -665,9 +1227,9 @@
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B7">
         <v>27.26</v>
@@ -691,12 +1253,12 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="B8">
-        <v>77.79000000000001</v>
+        <v>77.790000000000006</v>
       </c>
       <c r="C8">
         <v>14.41</v>
@@ -708,7 +1270,7 @@
         <v>36</v>
       </c>
       <c r="F8">
-        <v>87.90000000000001</v>
+        <v>87.9</v>
       </c>
       <c r="G8">
         <v>18</v>
@@ -717,9 +1279,9 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B9">
         <v>44.13</v>
@@ -734,7 +1296,7 @@
         <v>34</v>
       </c>
       <c r="F9">
-        <v>83.90000000000001</v>
+        <v>83.9</v>
       </c>
       <c r="G9">
         <v>59</v>
@@ -743,12 +1305,12 @@
         <v>37</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B10">
-        <v>65.68000000000001</v>
+        <v>65.680000000000007</v>
       </c>
       <c r="C10">
         <v>79.16</v>
@@ -760,7 +1322,7 @@
         <v>31</v>
       </c>
       <c r="F10">
-        <v>90.09999999999999</v>
+        <v>90.1</v>
       </c>
       <c r="G10">
         <v>49</v>
@@ -769,9 +1331,9 @@
         <v>37</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B11">
         <v>67.95</v>
@@ -786,7 +1348,7 @@
         <v>35</v>
       </c>
       <c r="F11">
-        <v>90.40000000000001</v>
+        <v>90.4</v>
       </c>
       <c r="G11">
         <v>9</v>
@@ -795,9 +1357,9 @@
         <v>39</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B12">
         <v>36.69</v>
@@ -821,12 +1383,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B13">
-        <v>82.23999999999999</v>
+        <v>82.24</v>
       </c>
       <c r="C13">
         <v>32.69</v>
@@ -847,9 +1409,9 @@
         <v>37</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="B14">
         <v>36.69</v>
@@ -873,9 +1435,9 @@
         <v>40</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B15">
         <v>47.45</v>
@@ -899,12 +1461,12 @@
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B16">
-        <v>65.68000000000001</v>
+        <v>65.680000000000007</v>
       </c>
       <c r="C16">
         <v>79.16</v>
@@ -916,7 +1478,7 @@
         <v>31</v>
       </c>
       <c r="F16">
-        <v>90.09999999999999</v>
+        <v>90.1</v>
       </c>
       <c r="G16">
         <v>49</v>
@@ -925,15 +1487,15 @@
         <v>37</v>
       </c>
     </row>
-    <row r="17" spans="1:8">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="B17">
-        <v>67.79000000000001</v>
+        <v>67.790000000000006</v>
       </c>
       <c r="C17">
-        <v>91.20999999999999</v>
+        <v>91.21</v>
       </c>
       <c r="D17">
         <v>0.87</v>
@@ -951,9 +1513,9 @@
         <v>38</v>
       </c>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B18">
         <v>96.16</v>
@@ -977,9 +1539,9 @@
         <v>40</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="B19">
         <v>47.94</v>
@@ -1003,12 +1565,12 @@
         <v>38</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="B20">
-        <v>82.23999999999999</v>
+        <v>82.24</v>
       </c>
       <c r="C20">
         <v>32.69</v>
@@ -1029,9 +1591,9 @@
         <v>37</v>
       </c>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="B21">
         <v>96.08</v>
@@ -1055,12 +1617,12 @@
         <v>38</v>
       </c>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="B22">
-        <v>36.88</v>
+        <v>36.880000000000003</v>
       </c>
       <c r="C22">
         <v>15.91</v>
@@ -1081,9 +1643,9 @@
         <v>38</v>
       </c>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="B23">
         <v>27.26</v>
@@ -1107,9 +1669,9 @@
         <v>38</v>
       </c>
     </row>
-    <row r="24" spans="1:8">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="B24">
         <v>70.86</v>
@@ -1118,7 +1680,7 @@
         <v>66.8</v>
       </c>
       <c r="D24">
-        <v>9.119999999999999</v>
+        <v>9.1199999999999992</v>
       </c>
       <c r="E24" t="s">
         <v>34</v>
@@ -1133,9 +1695,9 @@
         <v>41</v>
       </c>
     </row>
-    <row r="25" spans="1:8">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="B25">
         <v>29.9</v>
@@ -1144,7 +1706,7 @@
         <v>60.63</v>
       </c>
       <c r="D25">
-        <v>0.29</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="E25" t="s">
         <v>31</v>
@@ -1159,9 +1721,9 @@
         <v>37</v>
       </c>
     </row>
-    <row r="26" spans="1:8">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="B26">
         <v>96.08</v>
@@ -1185,9 +1747,9 @@
         <v>38</v>
       </c>
     </row>
-    <row r="27" spans="1:8">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="B27">
         <v>47.94</v>
@@ -1211,12 +1773,12 @@
         <v>38</v>
       </c>
     </row>
-    <row r="28" spans="1:8">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="B28">
-        <v>82.23999999999999</v>
+        <v>82.24</v>
       </c>
       <c r="C28">
         <v>32.69</v>
@@ -1237,12 +1799,12 @@
         <v>37</v>
       </c>
     </row>
-    <row r="29" spans="1:8">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="B29">
-        <v>36.88</v>
+        <v>36.880000000000003</v>
       </c>
       <c r="C29">
         <v>15.91</v>
@@ -1263,12 +1825,12 @@
         <v>38</v>
       </c>
     </row>
-    <row r="30" spans="1:8">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="B30">
-        <v>77.79000000000001</v>
+        <v>77.790000000000006</v>
       </c>
       <c r="C30">
         <v>14.41</v>
@@ -1280,7 +1842,7 @@
         <v>36</v>
       </c>
       <c r="F30">
-        <v>87.90000000000001</v>
+        <v>87.9</v>
       </c>
       <c r="G30">
         <v>18</v>
@@ -1289,12 +1851,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="31" spans="1:8">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>13</v>
+        <v>51</v>
       </c>
       <c r="B31">
-        <v>82.23999999999999</v>
+        <v>82.24</v>
       </c>
       <c r="C31">
         <v>32.69</v>
@@ -1315,9 +1877,9 @@
         <v>37</v>
       </c>
     </row>
-    <row r="32" spans="1:8">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="B32">
         <v>29.9</v>
@@ -1326,7 +1888,7 @@
         <v>60.63</v>
       </c>
       <c r="D32">
-        <v>0.29</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="E32" t="s">
         <v>31</v>
@@ -1341,15 +1903,15 @@
         <v>37</v>
       </c>
     </row>
-    <row r="33" spans="1:8">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="B33">
         <v>90.05</v>
       </c>
       <c r="C33">
-        <v>34.41</v>
+        <v>34.409999999999997</v>
       </c>
       <c r="D33">
         <v>31</v>
@@ -1367,12 +1929,12 @@
         <v>38</v>
       </c>
     </row>
-    <row r="34" spans="1:8">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>13</v>
+        <v>54</v>
       </c>
       <c r="B34">
-        <v>82.23999999999999</v>
+        <v>82.24</v>
       </c>
       <c r="C34">
         <v>32.69</v>
@@ -1393,9 +1955,9 @@
         <v>37</v>
       </c>
     </row>
-    <row r="35" spans="1:8">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="B35">
         <v>67.95</v>
@@ -1410,7 +1972,7 @@
         <v>35</v>
       </c>
       <c r="F35">
-        <v>90.40000000000001</v>
+        <v>90.4</v>
       </c>
       <c r="G35">
         <v>9</v>
@@ -1419,15 +1981,15 @@
         <v>39</v>
       </c>
     </row>
-    <row r="36" spans="1:8">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>12</v>
+        <v>56</v>
       </c>
       <c r="B36">
-        <v>67.79000000000001</v>
+        <v>67.790000000000006</v>
       </c>
       <c r="C36">
-        <v>91.20999999999999</v>
+        <v>91.21</v>
       </c>
       <c r="D36">
         <v>0.87</v>
@@ -1445,9 +2007,9 @@
         <v>38</v>
       </c>
     </row>
-    <row r="37" spans="1:8">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="B37">
         <v>47.94</v>
@@ -1471,12 +2033,12 @@
         <v>38</v>
       </c>
     </row>
-    <row r="38" spans="1:8">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="B38">
-        <v>36.88</v>
+        <v>36.880000000000003</v>
       </c>
       <c r="C38">
         <v>15.91</v>
@@ -1497,9 +2059,9 @@
         <v>38</v>
       </c>
     </row>
-    <row r="39" spans="1:8">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>22</v>
+        <v>59</v>
       </c>
       <c r="B39">
         <v>47.94</v>
@@ -1523,9 +2085,9 @@
         <v>38</v>
       </c>
     </row>
-    <row r="40" spans="1:8">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="B40">
         <v>47.94</v>
@@ -1549,9 +2111,9 @@
         <v>38</v>
       </c>
     </row>
-    <row r="41" spans="1:8">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>28</v>
+        <v>61</v>
       </c>
       <c r="B41">
         <v>85.63</v>
@@ -1575,9 +2137,9 @@
         <v>41</v>
       </c>
     </row>
-    <row r="42" spans="1:8">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>15</v>
+        <v>62</v>
       </c>
       <c r="B42">
         <v>27.17</v>
@@ -1601,12 +2163,12 @@
         <v>39</v>
       </c>
     </row>
-    <row r="43" spans="1:8">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>24</v>
+        <v>63</v>
       </c>
       <c r="B43">
-        <v>36.88</v>
+        <v>36.880000000000003</v>
       </c>
       <c r="C43">
         <v>15.91</v>
@@ -1627,9 +2189,9 @@
         <v>38</v>
       </c>
     </row>
-    <row r="44" spans="1:8">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>26</v>
+        <v>64</v>
       </c>
       <c r="B44">
         <v>29.9</v>
@@ -1638,7 +2200,7 @@
         <v>60.63</v>
       </c>
       <c r="D44">
-        <v>0.29</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="E44" t="s">
         <v>31</v>
@@ -1653,9 +2215,9 @@
         <v>37</v>
       </c>
     </row>
-    <row r="45" spans="1:8">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>22</v>
+        <v>65</v>
       </c>
       <c r="B45">
         <v>47.94</v>
@@ -1679,9 +2241,9 @@
         <v>38</v>
       </c>
     </row>
-    <row r="46" spans="1:8">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>28</v>
+        <v>66</v>
       </c>
       <c r="B46">
         <v>85.63</v>
@@ -1705,9 +2267,9 @@
         <v>41</v>
       </c>
     </row>
-    <row r="47" spans="1:8">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>20</v>
+        <v>67</v>
       </c>
       <c r="B47">
         <v>47.45</v>
@@ -1731,9 +2293,9 @@
         <v>38</v>
       </c>
     </row>
-    <row r="48" spans="1:8">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>29</v>
+        <v>68</v>
       </c>
       <c r="B48">
         <v>97.27</v>
@@ -1757,9 +2319,9 @@
         <v>38</v>
       </c>
     </row>
-    <row r="49" spans="1:8">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>22</v>
+        <v>69</v>
       </c>
       <c r="B49">
         <v>47.94</v>
@@ -1783,9 +2345,9 @@
         <v>38</v>
       </c>
     </row>
-    <row r="50" spans="1:8">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="B50">
         <v>67.95</v>
@@ -1800,7 +2362,7 @@
         <v>35</v>
       </c>
       <c r="F50">
-        <v>90.40000000000001</v>
+        <v>90.4</v>
       </c>
       <c r="G50">
         <v>9</v>
@@ -1809,9 +2371,9 @@
         <v>39</v>
       </c>
     </row>
-    <row r="51" spans="1:8">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>21</v>
+        <v>71</v>
       </c>
       <c r="B51">
         <v>96.16</v>
@@ -1835,9 +2397,9 @@
         <v>40</v>
       </c>
     </row>
-    <row r="52" spans="1:8">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>22</v>
+        <v>72</v>
       </c>
       <c r="B52">
         <v>47.94</v>
@@ -1861,12 +2423,12 @@
         <v>38</v>
       </c>
     </row>
-    <row r="53" spans="1:8">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>13</v>
+        <v>73</v>
       </c>
       <c r="B53">
-        <v>82.23999999999999</v>
+        <v>82.24</v>
       </c>
       <c r="C53">
         <v>32.69</v>
@@ -1887,9 +2449,9 @@
         <v>37</v>
       </c>
     </row>
-    <row r="54" spans="1:8">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>15</v>
+        <v>74</v>
       </c>
       <c r="B54">
         <v>27.17</v>
@@ -1913,9 +2475,9 @@
         <v>39</v>
       </c>
     </row>
-    <row r="55" spans="1:8">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>18</v>
+        <v>75</v>
       </c>
       <c r="B55">
         <v>67.95</v>
@@ -1930,7 +2492,7 @@
         <v>35</v>
       </c>
       <c r="F55">
-        <v>90.40000000000001</v>
+        <v>90.4</v>
       </c>
       <c r="G55">
         <v>9</v>
@@ -1939,9 +2501,9 @@
         <v>39</v>
       </c>
     </row>
-    <row r="56" spans="1:8">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>16</v>
+        <v>76</v>
       </c>
       <c r="B56">
         <v>27.26</v>
@@ -1965,9 +2527,9 @@
         <v>38</v>
       </c>
     </row>
-    <row r="57" spans="1:8">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>16</v>
+        <v>77</v>
       </c>
       <c r="B57">
         <v>27.26</v>
@@ -1991,9 +2553,9 @@
         <v>38</v>
       </c>
     </row>
-    <row r="58" spans="1:8">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>25</v>
+        <v>78</v>
       </c>
       <c r="B58">
         <v>70.86</v>
@@ -2002,7 +2564,7 @@
         <v>66.8</v>
       </c>
       <c r="D58">
-        <v>9.119999999999999</v>
+        <v>9.1199999999999992</v>
       </c>
       <c r="E58" t="s">
         <v>34</v>
@@ -2017,9 +2579,9 @@
         <v>41</v>
       </c>
     </row>
-    <row r="59" spans="1:8">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>22</v>
+        <v>79</v>
       </c>
       <c r="B59">
         <v>47.94</v>
@@ -2043,9 +2605,9 @@
         <v>38</v>
       </c>
     </row>
-    <row r="60" spans="1:8">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>18</v>
+        <v>80</v>
       </c>
       <c r="B60">
         <v>67.95</v>
@@ -2060,7 +2622,7 @@
         <v>35</v>
       </c>
       <c r="F60">
-        <v>90.40000000000001</v>
+        <v>90.4</v>
       </c>
       <c r="G60">
         <v>9</v>
@@ -2069,12 +2631,12 @@
         <v>39</v>
       </c>
     </row>
-    <row r="61" spans="1:8">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>11</v>
+        <v>81</v>
       </c>
       <c r="B61">
-        <v>65.68000000000001</v>
+        <v>65.680000000000007</v>
       </c>
       <c r="C61">
         <v>79.16</v>
@@ -2086,7 +2648,7 @@
         <v>31</v>
       </c>
       <c r="F61">
-        <v>90.09999999999999</v>
+        <v>90.1</v>
       </c>
       <c r="G61">
         <v>49</v>
@@ -2095,12 +2657,12 @@
         <v>37</v>
       </c>
     </row>
-    <row r="62" spans="1:8">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>24</v>
+        <v>82</v>
       </c>
       <c r="B62">
-        <v>36.88</v>
+        <v>36.880000000000003</v>
       </c>
       <c r="C62">
         <v>15.91</v>
@@ -2121,15 +2683,15 @@
         <v>38</v>
       </c>
     </row>
-    <row r="63" spans="1:8">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>12</v>
+        <v>83</v>
       </c>
       <c r="B63">
-        <v>67.79000000000001</v>
+        <v>67.790000000000006</v>
       </c>
       <c r="C63">
-        <v>91.20999999999999</v>
+        <v>91.21</v>
       </c>
       <c r="D63">
         <v>0.87</v>
@@ -2147,12 +2709,12 @@
         <v>38</v>
       </c>
     </row>
-    <row r="64" spans="1:8">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>13</v>
+        <v>84</v>
       </c>
       <c r="B64">
-        <v>82.23999999999999</v>
+        <v>82.24</v>
       </c>
       <c r="C64">
         <v>32.69</v>
@@ -2173,9 +2735,9 @@
         <v>37</v>
       </c>
     </row>
-    <row r="65" spans="1:8">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>30</v>
+        <v>85</v>
       </c>
       <c r="B65">
         <v>69.12</v>
@@ -2199,9 +2761,9 @@
         <v>41</v>
       </c>
     </row>
-    <row r="66" spans="1:8">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="B66">
         <v>47.45</v>
@@ -2225,9 +2787,9 @@
         <v>38</v>
       </c>
     </row>
-    <row r="67" spans="1:8">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="B67">
         <v>47.45</v>
@@ -2251,12 +2813,12 @@
         <v>38</v>
       </c>
     </row>
-    <row r="68" spans="1:8">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>24</v>
+        <v>88</v>
       </c>
       <c r="B68">
-        <v>36.88</v>
+        <v>36.880000000000003</v>
       </c>
       <c r="C68">
         <v>15.91</v>
@@ -2277,9 +2839,9 @@
         <v>38</v>
       </c>
     </row>
-    <row r="69" spans="1:8">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>22</v>
+        <v>89</v>
       </c>
       <c r="B69">
         <v>47.94</v>
@@ -2303,9 +2865,9 @@
         <v>38</v>
       </c>
     </row>
-    <row r="70" spans="1:8">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>28</v>
+        <v>90</v>
       </c>
       <c r="B70">
         <v>85.63</v>
@@ -2329,15 +2891,15 @@
         <v>41</v>
       </c>
     </row>
-    <row r="71" spans="1:8">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>27</v>
+        <v>91</v>
       </c>
       <c r="B71">
         <v>90.05</v>
       </c>
       <c r="C71">
-        <v>34.41</v>
+        <v>34.409999999999997</v>
       </c>
       <c r="D71">
         <v>31</v>
@@ -2355,12 +2917,12 @@
         <v>38</v>
       </c>
     </row>
-    <row r="72" spans="1:8">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>13</v>
+        <v>92</v>
       </c>
       <c r="B72">
-        <v>82.23999999999999</v>
+        <v>82.24</v>
       </c>
       <c r="C72">
         <v>32.69</v>
@@ -2381,12 +2943,12 @@
         <v>37</v>
       </c>
     </row>
-    <row r="73" spans="1:8">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>13</v>
+        <v>93</v>
       </c>
       <c r="B73">
-        <v>82.23999999999999</v>
+        <v>82.24</v>
       </c>
       <c r="C73">
         <v>32.69</v>
@@ -2407,9 +2969,9 @@
         <v>37</v>
       </c>
     </row>
-    <row r="74" spans="1:8">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>19</v>
+        <v>94</v>
       </c>
       <c r="B74">
         <v>36.69</v>
@@ -2433,12 +2995,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="75" spans="1:8">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>13</v>
+        <v>95</v>
       </c>
       <c r="B75">
-        <v>82.23999999999999</v>
+        <v>82.24</v>
       </c>
       <c r="C75">
         <v>32.69</v>
@@ -2459,9 +3021,9 @@
         <v>37</v>
       </c>
     </row>
-    <row r="76" spans="1:8">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>22</v>
+        <v>96</v>
       </c>
       <c r="B76">
         <v>47.94</v>
@@ -2485,9 +3047,9 @@
         <v>38</v>
       </c>
     </row>
-    <row r="77" spans="1:8">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>23</v>
+        <v>97</v>
       </c>
       <c r="B77">
         <v>96.08</v>
@@ -2511,15 +3073,15 @@
         <v>38</v>
       </c>
     </row>
-    <row r="78" spans="1:8">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>12</v>
+        <v>98</v>
       </c>
       <c r="B78">
-        <v>67.79000000000001</v>
+        <v>67.790000000000006</v>
       </c>
       <c r="C78">
-        <v>91.20999999999999</v>
+        <v>91.21</v>
       </c>
       <c r="D78">
         <v>0.87</v>
@@ -2537,12 +3099,12 @@
         <v>38</v>
       </c>
     </row>
-    <row r="79" spans="1:8">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>17</v>
+        <v>99</v>
       </c>
       <c r="B79">
-        <v>77.79000000000001</v>
+        <v>77.790000000000006</v>
       </c>
       <c r="C79">
         <v>14.41</v>
@@ -2554,7 +3116,7 @@
         <v>36</v>
       </c>
       <c r="F79">
-        <v>87.90000000000001</v>
+        <v>87.9</v>
       </c>
       <c r="G79">
         <v>18</v>
@@ -2563,12 +3125,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="80" spans="1:8">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>17</v>
+        <v>100</v>
       </c>
       <c r="B80">
-        <v>77.79000000000001</v>
+        <v>77.790000000000006</v>
       </c>
       <c r="C80">
         <v>14.41</v>
@@ -2580,7 +3142,7 @@
         <v>36</v>
       </c>
       <c r="F80">
-        <v>87.90000000000001</v>
+        <v>87.9</v>
       </c>
       <c r="G80">
         <v>18</v>
@@ -2589,12 +3151,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="81" spans="1:8">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>17</v>
+        <v>101</v>
       </c>
       <c r="B81">
-        <v>77.79000000000001</v>
+        <v>77.790000000000006</v>
       </c>
       <c r="C81">
         <v>14.41</v>
@@ -2606,7 +3168,7 @@
         <v>36</v>
       </c>
       <c r="F81">
-        <v>87.90000000000001</v>
+        <v>87.9</v>
       </c>
       <c r="G81">
         <v>18</v>
@@ -2615,12 +3177,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="82" spans="1:8">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>11</v>
+        <v>102</v>
       </c>
       <c r="B82">
-        <v>65.68000000000001</v>
+        <v>65.680000000000007</v>
       </c>
       <c r="C82">
         <v>79.16</v>
@@ -2632,7 +3194,7 @@
         <v>31</v>
       </c>
       <c r="F82">
-        <v>90.09999999999999</v>
+        <v>90.1</v>
       </c>
       <c r="G82">
         <v>49</v>
@@ -2641,9 +3203,9 @@
         <v>37</v>
       </c>
     </row>
-    <row r="83" spans="1:8">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>28</v>
+        <v>103</v>
       </c>
       <c r="B83">
         <v>85.63</v>
@@ -2667,9 +3229,9 @@
         <v>41</v>
       </c>
     </row>
-    <row r="84" spans="1:8">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>23</v>
+        <v>104</v>
       </c>
       <c r="B84">
         <v>96.08</v>
@@ -2693,15 +3255,15 @@
         <v>38</v>
       </c>
     </row>
-    <row r="85" spans="1:8">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>12</v>
+        <v>105</v>
       </c>
       <c r="B85">
-        <v>67.79000000000001</v>
+        <v>67.790000000000006</v>
       </c>
       <c r="C85">
-        <v>91.20999999999999</v>
+        <v>91.21</v>
       </c>
       <c r="D85">
         <v>0.87</v>
@@ -2719,15 +3281,15 @@
         <v>38</v>
       </c>
     </row>
-    <row r="86" spans="1:8">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>27</v>
+        <v>106</v>
       </c>
       <c r="B86">
         <v>90.05</v>
       </c>
       <c r="C86">
-        <v>34.41</v>
+        <v>34.409999999999997</v>
       </c>
       <c r="D86">
         <v>31</v>
@@ -2745,9 +3307,9 @@
         <v>38</v>
       </c>
     </row>
-    <row r="87" spans="1:8">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>14</v>
+        <v>107</v>
       </c>
       <c r="B87">
         <v>44.13</v>
@@ -2762,7 +3324,7 @@
         <v>34</v>
       </c>
       <c r="F87">
-        <v>83.90000000000001</v>
+        <v>83.9</v>
       </c>
       <c r="G87">
         <v>59</v>
@@ -2771,12 +3333,12 @@
         <v>37</v>
       </c>
     </row>
-    <row r="88" spans="1:8">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>13</v>
+        <v>108</v>
       </c>
       <c r="B88">
-        <v>82.23999999999999</v>
+        <v>82.24</v>
       </c>
       <c r="C88">
         <v>32.69</v>
@@ -2797,9 +3359,9 @@
         <v>37</v>
       </c>
     </row>
-    <row r="89" spans="1:8">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>22</v>
+        <v>109</v>
       </c>
       <c r="B89">
         <v>47.94</v>
@@ -2823,9 +3385,9 @@
         <v>38</v>
       </c>
     </row>
-    <row r="90" spans="1:8">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>29</v>
+        <v>110</v>
       </c>
       <c r="B90">
         <v>97.27</v>
@@ -2849,9 +3411,9 @@
         <v>38</v>
       </c>
     </row>
-    <row r="91" spans="1:8">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>25</v>
+        <v>111</v>
       </c>
       <c r="B91">
         <v>70.86</v>
@@ -2860,7 +3422,7 @@
         <v>66.8</v>
       </c>
       <c r="D91">
-        <v>9.119999999999999</v>
+        <v>9.1199999999999992</v>
       </c>
       <c r="E91" t="s">
         <v>34</v>
@@ -2875,9 +3437,9 @@
         <v>41</v>
       </c>
     </row>
-    <row r="92" spans="1:8">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>15</v>
+        <v>112</v>
       </c>
       <c r="B92">
         <v>27.17</v>
@@ -2901,12 +3463,12 @@
         <v>39</v>
       </c>
     </row>
-    <row r="93" spans="1:8">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>24</v>
+        <v>113</v>
       </c>
       <c r="B93">
-        <v>36.88</v>
+        <v>36.880000000000003</v>
       </c>
       <c r="C93">
         <v>15.91</v>
@@ -2927,9 +3489,9 @@
         <v>38</v>
       </c>
     </row>
-    <row r="94" spans="1:8">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>26</v>
+        <v>114</v>
       </c>
       <c r="B94">
         <v>29.9</v>
@@ -2938,7 +3500,7 @@
         <v>60.63</v>
       </c>
       <c r="D94">
-        <v>0.29</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="E94" t="s">
         <v>31</v>
@@ -2953,12 +3515,12 @@
         <v>37</v>
       </c>
     </row>
-    <row r="95" spans="1:8">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>13</v>
+        <v>115</v>
       </c>
       <c r="B95">
-        <v>82.23999999999999</v>
+        <v>82.24</v>
       </c>
       <c r="C95">
         <v>32.69</v>
@@ -2979,12 +3541,12 @@
         <v>37</v>
       </c>
     </row>
-    <row r="96" spans="1:8">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>17</v>
+        <v>116</v>
       </c>
       <c r="B96">
-        <v>77.79000000000001</v>
+        <v>77.790000000000006</v>
       </c>
       <c r="C96">
         <v>14.41</v>
@@ -2996,7 +3558,7 @@
         <v>36</v>
       </c>
       <c r="F96">
-        <v>87.90000000000001</v>
+        <v>87.9</v>
       </c>
       <c r="G96">
         <v>18</v>
@@ -3005,12 +3567,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="97" spans="1:8">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>24</v>
+        <v>117</v>
       </c>
       <c r="B97">
-        <v>36.88</v>
+        <v>36.880000000000003</v>
       </c>
       <c r="C97">
         <v>15.91</v>
@@ -3031,9 +3593,9 @@
         <v>38</v>
       </c>
     </row>
-    <row r="98" spans="1:8">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>28</v>
+        <v>118</v>
       </c>
       <c r="B98">
         <v>85.63</v>
@@ -3057,9 +3619,9 @@
         <v>41</v>
       </c>
     </row>
-    <row r="99" spans="1:8">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>14</v>
+        <v>119</v>
       </c>
       <c r="B99">
         <v>44.13</v>
@@ -3074,7 +3636,7 @@
         <v>34</v>
       </c>
       <c r="F99">
-        <v>83.90000000000001</v>
+        <v>83.9</v>
       </c>
       <c r="G99">
         <v>59</v>
@@ -3083,9 +3645,9 @@
         <v>37</v>
       </c>
     </row>
-    <row r="100" spans="1:8">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>16</v>
+        <v>120</v>
       </c>
       <c r="B100">
         <v>27.26</v>
@@ -3109,9 +3671,9 @@
         <v>38</v>
       </c>
     </row>
-    <row r="101" spans="1:8">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>20</v>
+        <v>121</v>
       </c>
       <c r="B101">
         <v>47.45</v>
@@ -3135,12 +3697,12 @@
         <v>38</v>
       </c>
     </row>
-    <row r="102" spans="1:8">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>13</v>
+        <v>122</v>
       </c>
       <c r="B102">
-        <v>82.23999999999999</v>
+        <v>82.24</v>
       </c>
       <c r="C102">
         <v>32.69</v>
@@ -3161,9 +3723,9 @@
         <v>37</v>
       </c>
     </row>
-    <row r="103" spans="1:8">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>25</v>
+        <v>123</v>
       </c>
       <c r="B103">
         <v>70.86</v>
@@ -3172,7 +3734,7 @@
         <v>66.8</v>
       </c>
       <c r="D103">
-        <v>9.119999999999999</v>
+        <v>9.1199999999999992</v>
       </c>
       <c r="E103" t="s">
         <v>34</v>
@@ -3187,9 +3749,9 @@
         <v>41</v>
       </c>
     </row>
-    <row r="104" spans="1:8">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>26</v>
+        <v>124</v>
       </c>
       <c r="B104">
         <v>29.9</v>
@@ -3198,7 +3760,7 @@
         <v>60.63</v>
       </c>
       <c r="D104">
-        <v>0.29</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="E104" t="s">
         <v>31</v>
@@ -3213,15 +3775,15 @@
         <v>37</v>
       </c>
     </row>
-    <row r="105" spans="1:8">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>27</v>
+        <v>125</v>
       </c>
       <c r="B105">
         <v>90.05</v>
       </c>
       <c r="C105">
-        <v>34.41</v>
+        <v>34.409999999999997</v>
       </c>
       <c r="D105">
         <v>31</v>
@@ -3239,15 +3801,15 @@
         <v>38</v>
       </c>
     </row>
-    <row r="106" spans="1:8">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>27</v>
+        <v>126</v>
       </c>
       <c r="B106">
         <v>90.05</v>
       </c>
       <c r="C106">
-        <v>34.41</v>
+        <v>34.409999999999997</v>
       </c>
       <c r="D106">
         <v>31</v>
@@ -3265,9 +3827,9 @@
         <v>38</v>
       </c>
     </row>
-    <row r="107" spans="1:8">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>14</v>
+        <v>127</v>
       </c>
       <c r="B107">
         <v>44.13</v>
@@ -3282,7 +3844,7 @@
         <v>34</v>
       </c>
       <c r="F107">
-        <v>83.90000000000001</v>
+        <v>83.9</v>
       </c>
       <c r="G107">
         <v>59</v>
@@ -3291,9 +3853,9 @@
         <v>37</v>
       </c>
     </row>
-    <row r="108" spans="1:8">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>22</v>
+        <v>128</v>
       </c>
       <c r="B108">
         <v>47.94</v>
@@ -3317,9 +3879,9 @@
         <v>38</v>
       </c>
     </row>
-    <row r="109" spans="1:8">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>16</v>
+        <v>129</v>
       </c>
       <c r="B109">
         <v>27.26</v>
@@ -3343,15 +3905,15 @@
         <v>38</v>
       </c>
     </row>
-    <row r="110" spans="1:8">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>27</v>
+        <v>130</v>
       </c>
       <c r="B110">
         <v>90.05</v>
       </c>
       <c r="C110">
-        <v>34.41</v>
+        <v>34.409999999999997</v>
       </c>
       <c r="D110">
         <v>31</v>
@@ -3369,9 +3931,9 @@
         <v>38</v>
       </c>
     </row>
-    <row r="111" spans="1:8">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>23</v>
+        <v>131</v>
       </c>
       <c r="B111">
         <v>96.08</v>
@@ -3395,9 +3957,9 @@
         <v>38</v>
       </c>
     </row>
-    <row r="112" spans="1:8">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>14</v>
+        <v>132</v>
       </c>
       <c r="B112">
         <v>44.13</v>
@@ -3412,7 +3974,7 @@
         <v>34</v>
       </c>
       <c r="F112">
-        <v>83.90000000000001</v>
+        <v>83.9</v>
       </c>
       <c r="G112">
         <v>59</v>
@@ -3421,15 +3983,15 @@
         <v>37</v>
       </c>
     </row>
-    <row r="113" spans="1:8">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>12</v>
+        <v>133</v>
       </c>
       <c r="B113">
-        <v>67.79000000000001</v>
+        <v>67.790000000000006</v>
       </c>
       <c r="C113">
-        <v>91.20999999999999</v>
+        <v>91.21</v>
       </c>
       <c r="D113">
         <v>0.87</v>
@@ -3447,9 +4009,9 @@
         <v>38</v>
       </c>
     </row>
-    <row r="114" spans="1:8">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>26</v>
+        <v>134</v>
       </c>
       <c r="B114">
         <v>29.9</v>
@@ -3458,7 +4020,7 @@
         <v>60.63</v>
       </c>
       <c r="D114">
-        <v>0.29</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="E114" t="s">
         <v>31</v>
@@ -3473,9 +4035,9 @@
         <v>37</v>
       </c>
     </row>
-    <row r="115" spans="1:8">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>25</v>
+        <v>135</v>
       </c>
       <c r="B115">
         <v>70.86</v>
@@ -3484,7 +4046,7 @@
         <v>66.8</v>
       </c>
       <c r="D115">
-        <v>9.119999999999999</v>
+        <v>9.1199999999999992</v>
       </c>
       <c r="E115" t="s">
         <v>34</v>
@@ -3499,9 +4061,9 @@
         <v>41</v>
       </c>
     </row>
-    <row r="116" spans="1:8">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>23</v>
+        <v>136</v>
       </c>
       <c r="B116">
         <v>96.08</v>
@@ -3525,9 +4087,9 @@
         <v>38</v>
       </c>
     </row>
-    <row r="117" spans="1:8">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>20</v>
+        <v>137</v>
       </c>
       <c r="B117">
         <v>47.45</v>
@@ -3551,9 +4113,9 @@
         <v>38</v>
       </c>
     </row>
-    <row r="118" spans="1:8">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>22</v>
+        <v>138</v>
       </c>
       <c r="B118">
         <v>47.94</v>
@@ -3577,9 +4139,9 @@
         <v>38</v>
       </c>
     </row>
-    <row r="119" spans="1:8">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>23</v>
+        <v>139</v>
       </c>
       <c r="B119">
         <v>96.08</v>
@@ -3603,9 +4165,9 @@
         <v>38</v>
       </c>
     </row>
-    <row r="120" spans="1:8">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>15</v>
+        <v>140</v>
       </c>
       <c r="B120">
         <v>27.17</v>
@@ -3629,9 +4191,9 @@
         <v>39</v>
       </c>
     </row>
-    <row r="121" spans="1:8">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>22</v>
+        <v>141</v>
       </c>
       <c r="B121">
         <v>47.94</v>
@@ -3655,15 +4217,15 @@
         <v>38</v>
       </c>
     </row>
-    <row r="122" spans="1:8">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>27</v>
+        <v>142</v>
       </c>
       <c r="B122">
         <v>90.05</v>
       </c>
       <c r="C122">
-        <v>34.41</v>
+        <v>34.409999999999997</v>
       </c>
       <c r="D122">
         <v>31</v>
@@ -3681,9 +4243,9 @@
         <v>38</v>
       </c>
     </row>
-    <row r="123" spans="1:8">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>20</v>
+        <v>143</v>
       </c>
       <c r="B123">
         <v>47.45</v>
@@ -3707,9 +4269,9 @@
         <v>38</v>
       </c>
     </row>
-    <row r="124" spans="1:8">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>14</v>
+        <v>144</v>
       </c>
       <c r="B124">
         <v>44.13</v>
@@ -3724,7 +4286,7 @@
         <v>34</v>
       </c>
       <c r="F124">
-        <v>83.90000000000001</v>
+        <v>83.9</v>
       </c>
       <c r="G124">
         <v>59</v>
@@ -3733,9 +4295,9 @@
         <v>37</v>
       </c>
     </row>
-    <row r="125" spans="1:8">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>22</v>
+        <v>145</v>
       </c>
       <c r="B125">
         <v>47.94</v>
@@ -3759,12 +4321,12 @@
         <v>38</v>
       </c>
     </row>
-    <row r="126" spans="1:8">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>24</v>
+        <v>146</v>
       </c>
       <c r="B126">
-        <v>36.88</v>
+        <v>36.880000000000003</v>
       </c>
       <c r="C126">
         <v>15.91</v>
@@ -3785,9 +4347,9 @@
         <v>38</v>
       </c>
     </row>
-    <row r="127" spans="1:8">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>14</v>
+        <v>147</v>
       </c>
       <c r="B127">
         <v>44.13</v>
@@ -3802,7 +4364,7 @@
         <v>34</v>
       </c>
       <c r="F127">
-        <v>83.90000000000001</v>
+        <v>83.9</v>
       </c>
       <c r="G127">
         <v>59</v>
@@ -3811,9 +4373,9 @@
         <v>37</v>
       </c>
     </row>
-    <row r="128" spans="1:8">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>26</v>
+        <v>148</v>
       </c>
       <c r="B128">
         <v>29.9</v>
@@ -3822,7 +4384,7 @@
         <v>60.63</v>
       </c>
       <c r="D128">
-        <v>0.29</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="E128" t="s">
         <v>31</v>
@@ -3837,9 +4399,9 @@
         <v>37</v>
       </c>
     </row>
-    <row r="129" spans="1:8">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>19</v>
+        <v>149</v>
       </c>
       <c r="B129">
         <v>36.69</v>
@@ -3863,9 +4425,9 @@
         <v>40</v>
       </c>
     </row>
-    <row r="130" spans="1:8">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>23</v>
+        <v>150</v>
       </c>
       <c r="B130">
         <v>96.08</v>
@@ -3889,9 +4451,9 @@
         <v>38</v>
       </c>
     </row>
-    <row r="131" spans="1:8">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>14</v>
+        <v>151</v>
       </c>
       <c r="B131">
         <v>44.13</v>
@@ -3906,7 +4468,7 @@
         <v>34</v>
       </c>
       <c r="F131">
-        <v>83.90000000000001</v>
+        <v>83.9</v>
       </c>
       <c r="G131">
         <v>59</v>
@@ -3915,9 +4477,9 @@
         <v>37</v>
       </c>
     </row>
-    <row r="132" spans="1:8">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>15</v>
+        <v>152</v>
       </c>
       <c r="B132">
         <v>27.17</v>
@@ -3941,9 +4503,9 @@
         <v>39</v>
       </c>
     </row>
-    <row r="133" spans="1:8">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>22</v>
+        <v>153</v>
       </c>
       <c r="B133">
         <v>47.94</v>
@@ -3967,9 +4529,9 @@
         <v>38</v>
       </c>
     </row>
-    <row r="134" spans="1:8">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>19</v>
+        <v>154</v>
       </c>
       <c r="B134">
         <v>36.69</v>
@@ -3993,12 +4555,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="135" spans="1:8">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>24</v>
+        <v>155</v>
       </c>
       <c r="B135">
-        <v>36.88</v>
+        <v>36.880000000000003</v>
       </c>
       <c r="C135">
         <v>15.91</v>
@@ -4019,9 +4581,9 @@
         <v>38</v>
       </c>
     </row>
-    <row r="136" spans="1:8">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>15</v>
+        <v>156</v>
       </c>
       <c r="B136">
         <v>27.17</v>
@@ -4045,12 +4607,12 @@
         <v>39</v>
       </c>
     </row>
-    <row r="137" spans="1:8">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>24</v>
+        <v>157</v>
       </c>
       <c r="B137">
-        <v>36.88</v>
+        <v>36.880000000000003</v>
       </c>
       <c r="C137">
         <v>15.91</v>
@@ -4071,9 +4633,9 @@
         <v>38</v>
       </c>
     </row>
-    <row r="138" spans="1:8">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>23</v>
+        <v>158</v>
       </c>
       <c r="B138">
         <v>96.08</v>
@@ -4097,12 +4659,12 @@
         <v>38</v>
       </c>
     </row>
-    <row r="139" spans="1:8">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>13</v>
+        <v>159</v>
       </c>
       <c r="B139">
-        <v>82.23999999999999</v>
+        <v>82.24</v>
       </c>
       <c r="C139">
         <v>32.69</v>
@@ -4123,12 +4685,12 @@
         <v>37</v>
       </c>
     </row>
-    <row r="140" spans="1:8">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>13</v>
+        <v>160</v>
       </c>
       <c r="B140">
-        <v>82.23999999999999</v>
+        <v>82.24</v>
       </c>
       <c r="C140">
         <v>32.69</v>
@@ -4149,12 +4711,12 @@
         <v>37</v>
       </c>
     </row>
-    <row r="141" spans="1:8">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>13</v>
+        <v>161</v>
       </c>
       <c r="B141">
-        <v>82.23999999999999</v>
+        <v>82.24</v>
       </c>
       <c r="C141">
         <v>32.69</v>
@@ -4175,9 +4737,9 @@
         <v>37</v>
       </c>
     </row>
-    <row r="142" spans="1:8">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>21</v>
+        <v>162</v>
       </c>
       <c r="B142">
         <v>96.16</v>
@@ -4201,9 +4763,9 @@
         <v>40</v>
       </c>
     </row>
-    <row r="143" spans="1:8">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>29</v>
+        <v>163</v>
       </c>
       <c r="B143">
         <v>97.27</v>
@@ -4227,9 +4789,9 @@
         <v>38</v>
       </c>
     </row>
-    <row r="144" spans="1:8">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>21</v>
+        <v>164</v>
       </c>
       <c r="B144">
         <v>96.16</v>
@@ -4253,9 +4815,9 @@
         <v>40</v>
       </c>
     </row>
-    <row r="145" spans="1:8">
+    <row r="145" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>30</v>
+        <v>165</v>
       </c>
       <c r="B145">
         <v>69.12</v>
@@ -4279,9 +4841,9 @@
         <v>41</v>
       </c>
     </row>
-    <row r="146" spans="1:8">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>20</v>
+        <v>166</v>
       </c>
       <c r="B146">
         <v>47.45</v>
@@ -4305,12 +4867,12 @@
         <v>38</v>
       </c>
     </row>
-    <row r="147" spans="1:8">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>17</v>
+        <v>167</v>
       </c>
       <c r="B147">
-        <v>77.79000000000001</v>
+        <v>77.790000000000006</v>
       </c>
       <c r="C147">
         <v>14.41</v>
@@ -4322,7 +4884,7 @@
         <v>36</v>
       </c>
       <c r="F147">
-        <v>87.90000000000001</v>
+        <v>87.9</v>
       </c>
       <c r="G147">
         <v>18</v>
@@ -4331,9 +4893,9 @@
         <v>40</v>
       </c>
     </row>
-    <row r="148" spans="1:8">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>20</v>
+        <v>168</v>
       </c>
       <c r="B148">
         <v>47.45</v>
@@ -4357,9 +4919,9 @@
         <v>38</v>
       </c>
     </row>
-    <row r="149" spans="1:8">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>25</v>
+        <v>169</v>
       </c>
       <c r="B149">
         <v>70.86</v>
@@ -4368,7 +4930,7 @@
         <v>66.8</v>
       </c>
       <c r="D149">
-        <v>9.119999999999999</v>
+        <v>9.1199999999999992</v>
       </c>
       <c r="E149" t="s">
         <v>34</v>
@@ -4383,9 +4945,9 @@
         <v>41</v>
       </c>
     </row>
-    <row r="150" spans="1:8">
+    <row r="150" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>22</v>
+        <v>170</v>
       </c>
       <c r="B150">
         <v>47.94</v>
@@ -4409,9 +4971,9 @@
         <v>38</v>
       </c>
     </row>
-    <row r="151" spans="1:8">
+    <row r="151" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>15</v>
+        <v>171</v>
       </c>
       <c r="B151">
         <v>27.17</v>
@@ -4435,9 +4997,9 @@
         <v>39</v>
       </c>
     </row>
-    <row r="152" spans="1:8">
+    <row r="152" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>22</v>
+        <v>172</v>
       </c>
       <c r="B152">
         <v>47.94</v>
@@ -4461,15 +5023,15 @@
         <v>38</v>
       </c>
     </row>
-    <row r="153" spans="1:8">
+    <row r="153" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>27</v>
+        <v>173</v>
       </c>
       <c r="B153">
         <v>90.05</v>
       </c>
       <c r="C153">
-        <v>34.41</v>
+        <v>34.409999999999997</v>
       </c>
       <c r="D153">
         <v>31</v>
@@ -4487,9 +5049,9 @@
         <v>38</v>
       </c>
     </row>
-    <row r="154" spans="1:8">
+    <row r="154" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>21</v>
+        <v>174</v>
       </c>
       <c r="B154">
         <v>96.16</v>
@@ -4513,9 +5075,9 @@
         <v>40</v>
       </c>
     </row>
-    <row r="155" spans="1:8">
+    <row r="155" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>29</v>
+        <v>175</v>
       </c>
       <c r="B155">
         <v>97.27</v>
@@ -4539,12 +5101,12 @@
         <v>38</v>
       </c>
     </row>
-    <row r="156" spans="1:8">
+    <row r="156" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>24</v>
+        <v>176</v>
       </c>
       <c r="B156">
-        <v>36.88</v>
+        <v>36.880000000000003</v>
       </c>
       <c r="C156">
         <v>15.91</v>
@@ -4565,12 +5127,12 @@
         <v>38</v>
       </c>
     </row>
-    <row r="157" spans="1:8">
+    <row r="157" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>17</v>
+        <v>177</v>
       </c>
       <c r="B157">
-        <v>77.79000000000001</v>
+        <v>77.790000000000006</v>
       </c>
       <c r="C157">
         <v>14.41</v>
@@ -4582,7 +5144,7 @@
         <v>36</v>
       </c>
       <c r="F157">
-        <v>87.90000000000001</v>
+        <v>87.9</v>
       </c>
       <c r="G157">
         <v>18</v>
@@ -4591,12 +5153,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="158" spans="1:8">
+    <row r="158" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>11</v>
+        <v>178</v>
       </c>
       <c r="B158">
-        <v>65.68000000000001</v>
+        <v>65.680000000000007</v>
       </c>
       <c r="C158">
         <v>79.16</v>
@@ -4608,7 +5170,7 @@
         <v>31</v>
       </c>
       <c r="F158">
-        <v>90.09999999999999</v>
+        <v>90.1</v>
       </c>
       <c r="G158">
         <v>49</v>
@@ -4617,12 +5179,12 @@
         <v>37</v>
       </c>
     </row>
-    <row r="159" spans="1:8">
+    <row r="159" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>13</v>
+        <v>179</v>
       </c>
       <c r="B159">
-        <v>82.23999999999999</v>
+        <v>82.24</v>
       </c>
       <c r="C159">
         <v>32.69</v>
@@ -4643,9 +5205,9 @@
         <v>37</v>
       </c>
     </row>
-    <row r="160" spans="1:8">
+    <row r="160" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>28</v>
+        <v>180</v>
       </c>
       <c r="B160">
         <v>85.63</v>
@@ -4669,15 +5231,15 @@
         <v>41</v>
       </c>
     </row>
-    <row r="161" spans="1:8">
+    <row r="161" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>12</v>
+        <v>181</v>
       </c>
       <c r="B161">
-        <v>67.79000000000001</v>
+        <v>67.790000000000006</v>
       </c>
       <c r="C161">
-        <v>91.20999999999999</v>
+        <v>91.21</v>
       </c>
       <c r="D161">
         <v>0.87</v>
@@ -4695,9 +5257,9 @@
         <v>38</v>
       </c>
     </row>
-    <row r="162" spans="1:8">
+    <row r="162" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>26</v>
+        <v>182</v>
       </c>
       <c r="B162">
         <v>29.9</v>
@@ -4706,7 +5268,7 @@
         <v>60.63</v>
       </c>
       <c r="D162">
-        <v>0.29</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="E162" t="s">
         <v>31</v>
@@ -4721,15 +5283,15 @@
         <v>37</v>
       </c>
     </row>
-    <row r="163" spans="1:8">
+    <row r="163" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>12</v>
+        <v>183</v>
       </c>
       <c r="B163">
-        <v>67.79000000000001</v>
+        <v>67.790000000000006</v>
       </c>
       <c r="C163">
-        <v>91.20999999999999</v>
+        <v>91.21</v>
       </c>
       <c r="D163">
         <v>0.87</v>
@@ -4747,9 +5309,9 @@
         <v>38</v>
       </c>
     </row>
-    <row r="164" spans="1:8">
+    <row r="164" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>23</v>
+        <v>184</v>
       </c>
       <c r="B164">
         <v>96.08</v>
@@ -4773,9 +5335,9 @@
         <v>38</v>
       </c>
     </row>
-    <row r="165" spans="1:8">
+    <row r="165" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>21</v>
+        <v>185</v>
       </c>
       <c r="B165">
         <v>96.16</v>
@@ -4799,12 +5361,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="166" spans="1:8">
+    <row r="166" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>13</v>
+        <v>186</v>
       </c>
       <c r="B166">
-        <v>82.23999999999999</v>
+        <v>82.24</v>
       </c>
       <c r="C166">
         <v>32.69</v>
@@ -4825,9 +5387,9 @@
         <v>37</v>
       </c>
     </row>
-    <row r="167" spans="1:8">
+    <row r="167" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>23</v>
+        <v>187</v>
       </c>
       <c r="B167">
         <v>96.08</v>
@@ -4851,9 +5413,9 @@
         <v>38</v>
       </c>
     </row>
-    <row r="168" spans="1:8">
+    <row r="168" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>15</v>
+        <v>188</v>
       </c>
       <c r="B168">
         <v>27.17</v>
@@ -4877,12 +5439,12 @@
         <v>39</v>
       </c>
     </row>
-    <row r="169" spans="1:8">
+    <row r="169" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>17</v>
+        <v>189</v>
       </c>
       <c r="B169">
-        <v>77.79000000000001</v>
+        <v>77.790000000000006</v>
       </c>
       <c r="C169">
         <v>14.41</v>
@@ -4894,7 +5456,7 @@
         <v>36</v>
       </c>
       <c r="F169">
-        <v>87.90000000000001</v>
+        <v>87.9</v>
       </c>
       <c r="G169">
         <v>18</v>
@@ -4903,9 +5465,9 @@
         <v>40</v>
       </c>
     </row>
-    <row r="170" spans="1:8">
+    <row r="170" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>16</v>
+        <v>190</v>
       </c>
       <c r="B170">
         <v>27.26</v>
@@ -4929,9 +5491,9 @@
         <v>38</v>
       </c>
     </row>
-    <row r="171" spans="1:8">
+    <row r="171" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>16</v>
+        <v>191</v>
       </c>
       <c r="B171">
         <v>27.26</v>
@@ -4955,9 +5517,9 @@
         <v>38</v>
       </c>
     </row>
-    <row r="172" spans="1:8">
+    <row r="172" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>19</v>
+        <v>192</v>
       </c>
       <c r="B172">
         <v>36.69</v>
@@ -4981,9 +5543,9 @@
         <v>40</v>
       </c>
     </row>
-    <row r="173" spans="1:8">
+    <row r="173" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>14</v>
+        <v>193</v>
       </c>
       <c r="B173">
         <v>44.13</v>
@@ -4998,7 +5560,7 @@
         <v>34</v>
       </c>
       <c r="F173">
-        <v>83.90000000000001</v>
+        <v>83.9</v>
       </c>
       <c r="G173">
         <v>59</v>
@@ -5007,12 +5569,12 @@
         <v>37</v>
       </c>
     </row>
-    <row r="174" spans="1:8">
+    <row r="174" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>13</v>
+        <v>194</v>
       </c>
       <c r="B174">
-        <v>82.23999999999999</v>
+        <v>82.24</v>
       </c>
       <c r="C174">
         <v>32.69</v>
@@ -5033,9 +5595,9 @@
         <v>37</v>
       </c>
     </row>
-    <row r="175" spans="1:8">
+    <row r="175" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>28</v>
+        <v>195</v>
       </c>
       <c r="B175">
         <v>85.63</v>
@@ -5059,9 +5621,9 @@
         <v>41</v>
       </c>
     </row>
-    <row r="176" spans="1:8">
+    <row r="176" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>23</v>
+        <v>196</v>
       </c>
       <c r="B176">
         <v>96.08</v>
@@ -5085,15 +5647,15 @@
         <v>38</v>
       </c>
     </row>
-    <row r="177" spans="1:8">
+    <row r="177" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>27</v>
+        <v>197</v>
       </c>
       <c r="B177">
         <v>90.05</v>
       </c>
       <c r="C177">
-        <v>34.41</v>
+        <v>34.409999999999997</v>
       </c>
       <c r="D177">
         <v>31</v>
@@ -5111,9 +5673,9 @@
         <v>38</v>
       </c>
     </row>
-    <row r="178" spans="1:8">
+    <row r="178" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>22</v>
+        <v>198</v>
       </c>
       <c r="B178">
         <v>47.94</v>
@@ -5137,9 +5699,9 @@
         <v>38</v>
       </c>
     </row>
-    <row r="179" spans="1:8">
+    <row r="179" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>22</v>
+        <v>199</v>
       </c>
       <c r="B179">
         <v>47.94</v>
@@ -5163,9 +5725,9 @@
         <v>38</v>
       </c>
     </row>
-    <row r="180" spans="1:8">
+    <row r="180" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>19</v>
+        <v>200</v>
       </c>
       <c r="B180">
         <v>36.69</v>
@@ -5189,9 +5751,9 @@
         <v>40</v>
       </c>
     </row>
-    <row r="181" spans="1:8">
+    <row r="181" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>20</v>
+        <v>201</v>
       </c>
       <c r="B181">
         <v>47.45</v>
@@ -5215,12 +5777,12 @@
         <v>38</v>
       </c>
     </row>
-    <row r="182" spans="1:8">
+    <row r="182" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>24</v>
+        <v>202</v>
       </c>
       <c r="B182">
-        <v>36.88</v>
+        <v>36.880000000000003</v>
       </c>
       <c r="C182">
         <v>15.91</v>
@@ -5241,9 +5803,9 @@
         <v>38</v>
       </c>
     </row>
-    <row r="183" spans="1:8">
+    <row r="183" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>14</v>
+        <v>203</v>
       </c>
       <c r="B183">
         <v>44.13</v>
@@ -5258,7 +5820,7 @@
         <v>34</v>
       </c>
       <c r="F183">
-        <v>83.90000000000001</v>
+        <v>83.9</v>
       </c>
       <c r="G183">
         <v>59</v>
@@ -5267,9 +5829,9 @@
         <v>37</v>
       </c>
     </row>
-    <row r="184" spans="1:8">
+    <row r="184" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>21</v>
+        <v>204</v>
       </c>
       <c r="B184">
         <v>96.16</v>
@@ -5293,12 +5855,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="185" spans="1:8">
+    <row r="185" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>11</v>
+        <v>205</v>
       </c>
       <c r="B185">
-        <v>65.68000000000001</v>
+        <v>65.680000000000007</v>
       </c>
       <c r="C185">
         <v>79.16</v>
@@ -5310,7 +5872,7 @@
         <v>31</v>
       </c>
       <c r="F185">
-        <v>90.09999999999999</v>
+        <v>90.1</v>
       </c>
       <c r="G185">
         <v>49</v>
@@ -5319,9 +5881,9 @@
         <v>37</v>
       </c>
     </row>
-    <row r="186" spans="1:8">
+    <row r="186" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>26</v>
+        <v>206</v>
       </c>
       <c r="B186">
         <v>29.9</v>
@@ -5330,7 +5892,7 @@
         <v>60.63</v>
       </c>
       <c r="D186">
-        <v>0.29</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="E186" t="s">
         <v>31</v>
@@ -5345,9 +5907,9 @@
         <v>37</v>
       </c>
     </row>
-    <row r="187" spans="1:8">
+    <row r="187" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>19</v>
+        <v>207</v>
       </c>
       <c r="B187">
         <v>36.69</v>
@@ -5371,9 +5933,9 @@
         <v>40</v>
       </c>
     </row>
-    <row r="188" spans="1:8">
+    <row r="188" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>16</v>
+        <v>208</v>
       </c>
       <c r="B188">
         <v>27.26</v>
@@ -5397,9 +5959,9 @@
         <v>38</v>
       </c>
     </row>
-    <row r="189" spans="1:8">
+    <row r="189" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>18</v>
+        <v>209</v>
       </c>
       <c r="B189">
         <v>67.95</v>
@@ -5414,7 +5976,7 @@
         <v>35</v>
       </c>
       <c r="F189">
-        <v>90.40000000000001</v>
+        <v>90.4</v>
       </c>
       <c r="G189">
         <v>9</v>
@@ -5423,9 +5985,9 @@
         <v>39</v>
       </c>
     </row>
-    <row r="190" spans="1:8">
+    <row r="190" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>22</v>
+        <v>210</v>
       </c>
       <c r="B190">
         <v>47.94</v>
@@ -5449,9 +6011,9 @@
         <v>38</v>
       </c>
     </row>
-    <row r="191" spans="1:8">
+    <row r="191" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>22</v>
+        <v>211</v>
       </c>
       <c r="B191">
         <v>47.94</v>
@@ -5475,9 +6037,9 @@
         <v>38</v>
       </c>
     </row>
-    <row r="192" spans="1:8">
+    <row r="192" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>19</v>
+        <v>212</v>
       </c>
       <c r="B192">
         <v>36.69</v>
@@ -5501,9 +6063,9 @@
         <v>40</v>
       </c>
     </row>
-    <row r="193" spans="1:8">
+    <row r="193" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>19</v>
+        <v>213</v>
       </c>
       <c r="B193">
         <v>36.69</v>
@@ -5527,9 +6089,9 @@
         <v>40</v>
       </c>
     </row>
-    <row r="194" spans="1:8">
+    <row r="194" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>19</v>
+        <v>214</v>
       </c>
       <c r="B194">
         <v>36.69</v>
@@ -5553,9 +6115,9 @@
         <v>40</v>
       </c>
     </row>
-    <row r="195" spans="1:8">
+    <row r="195" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>22</v>
+        <v>215</v>
       </c>
       <c r="B195">
         <v>47.94</v>
@@ -5579,9 +6141,9 @@
         <v>38</v>
       </c>
     </row>
-    <row r="196" spans="1:8">
+    <row r="196" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>14</v>
+        <v>216</v>
       </c>
       <c r="B196">
         <v>44.13</v>
@@ -5596,7 +6158,7 @@
         <v>34</v>
       </c>
       <c r="F196">
-        <v>83.90000000000001</v>
+        <v>83.9</v>
       </c>
       <c r="G196">
         <v>59</v>
@@ -5605,12 +6167,12 @@
         <v>37</v>
       </c>
     </row>
-    <row r="197" spans="1:8">
+    <row r="197" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>13</v>
+        <v>217</v>
       </c>
       <c r="B197">
-        <v>82.23999999999999</v>
+        <v>82.24</v>
       </c>
       <c r="C197">
         <v>32.69</v>
@@ -5631,9 +6193,9 @@
         <v>37</v>
       </c>
     </row>
-    <row r="198" spans="1:8">
+    <row r="198" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>20</v>
+        <v>218</v>
       </c>
       <c r="B198">
         <v>47.45</v>
@@ -5657,12 +6219,12 @@
         <v>38</v>
       </c>
     </row>
-    <row r="199" spans="1:8">
+    <row r="199" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>13</v>
+        <v>219</v>
       </c>
       <c r="B199">
-        <v>82.23999999999999</v>
+        <v>82.24</v>
       </c>
       <c r="C199">
         <v>32.69</v>
@@ -5683,15 +6245,15 @@
         <v>37</v>
       </c>
     </row>
-    <row r="200" spans="1:8">
+    <row r="200" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>27</v>
+        <v>220</v>
       </c>
       <c r="B200">
         <v>90.05</v>
       </c>
       <c r="C200">
-        <v>34.41</v>
+        <v>34.409999999999997</v>
       </c>
       <c r="D200">
         <v>31</v>
@@ -5709,9 +6271,9 @@
         <v>38</v>
       </c>
     </row>
-    <row r="201" spans="1:8">
+    <row r="201" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>15</v>
+        <v>221</v>
       </c>
       <c r="B201">
         <v>27.17</v>
@@ -5736,6 +6298,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>